--- a/NBA/postplanner-imports/hh-postplanner-2026-09-04.xlsx
+++ b/NBA/postplanner-imports/hh-postplanner-2026-09-04.xlsx
@@ -478,7 +478,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/04/2026  11:50</t>
+          <t>09/04/2026  09:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/04/2026  13:17</t>
+          <t>09/04/2026  11:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -507,7 +507,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/04/2026  14:44</t>
+          <t>09/04/2026  11:05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,7 +522,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/04/2026  16:11</t>
+          <t>09/04/2026  13:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/04/2026  17:38</t>
+          <t>09/04/2026  13:05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -549,7 +549,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/04/2026  19:05</t>
+          <t>09/04/2026  16:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/04/2026  20:32</t>
+          <t>09/04/2026  19:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
